--- a/mobile-e2e/TEST_REPORT.xlsx
+++ b/mobile-e2e/TEST_REPORT.xlsx
@@ -415,7 +415,7 @@
         <v>Generated</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-02 23:13:14 UTC</v>
+        <v>2026-05-03 02:00:51 UTC</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v>Total Tests</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -455,7 +455,7 @@
         <v>Passed</v>
       </c>
       <c r="B8">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -463,7 +463,7 @@
         <v>Failed</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -471,7 +471,7 @@
         <v>Pass Rate</v>
       </c>
       <c r="B10" t="str">
-        <v>66%</v>
+        <v>62%</v>
       </c>
     </row>
     <row r="12">
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G38"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -639,19 +639,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>MODULE 6</v>
+        <v>MODULE 5</v>
       </c>
       <c r="B7" t="str">
-        <v>TC-ENG-001</v>
+        <v>TC-PLAY-005</v>
       </c>
       <c r="C7" t="str">
-        <v>Discover feed shows engagement surface</v>
+        <v>Listening History tracked after playback</v>
       </c>
       <c r="D7" t="str">
-        <v>FeedScreen &gt; Discover</v>
+        <v>LibraryScreen &gt; Listening History</v>
       </c>
       <c r="E7" t="str">
-        <v>VerticalFeedItem / Follow button / empty-state visible</v>
+        <v>Recently played tracks appear in Listening History list</v>
       </c>
       <c r="F7" t="str">
         <v>✅ PASSED</v>
@@ -665,16 +665,16 @@
         <v>MODULE 6</v>
       </c>
       <c r="B8" t="str">
-        <v>TC-ENG-002</v>
+        <v>TC-ENG-001</v>
       </c>
       <c r="C8" t="str">
-        <v>Track detail screen shows Comment bar</v>
+        <v>Discover feed shows engagement surface</v>
       </c>
       <c r="D8" t="str">
-        <v>LikedTracksScreen → TrackDetail</v>
+        <v>FeedScreen &gt; Discover</v>
       </c>
       <c r="E8" t="str">
-        <v>"Comment..." input visible</v>
+        <v>VerticalFeedItem / Follow button / empty-state visible</v>
       </c>
       <c r="F8" t="str">
         <v>✅ PASSED</v>
@@ -688,16 +688,16 @@
         <v>MODULE 6</v>
       </c>
       <c r="B9" t="str">
-        <v>TC-ENG-003</v>
+        <v>TC-ENG-002</v>
       </c>
       <c r="C9" t="str">
-        <v>Empty comment submission is blocked</v>
+        <v>Track detail screen shows Comment bar</v>
       </c>
       <c r="D9" t="str">
-        <v>TrackDetail</v>
+        <v>LikedTracksScreen → TrackDetail</v>
       </c>
       <c r="E9" t="str">
-        <v>Snackbar or hint prevents empty comment</v>
+        <v>"Comment..." input visible</v>
       </c>
       <c r="F9" t="str">
         <v>✅ PASSED</v>
@@ -708,140 +708,140 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>MODULE 7</v>
+        <v>MODULE 6</v>
       </c>
       <c r="B10" t="str">
-        <v>TC-PLY-001</v>
+        <v>TC-ENG-003</v>
       </c>
       <c r="C10" t="str">
-        <v>Playlists section exists in Library</v>
+        <v>Empty comment submission is blocked</v>
       </c>
       <c r="D10" t="str">
-        <v>LibraryScreen</v>
+        <v>TrackDetail</v>
       </c>
       <c r="E10" t="str">
-        <v>"Playlists" / "Sets" / "Collections" section visible</v>
+        <v>Snackbar or hint prevents empty comment</v>
       </c>
       <c r="F10" t="str">
-        <v>❌ FAILED</v>
+        <v>✅ PASSED</v>
       </c>
       <c r="G10" t="str">
-        <v>Playlists section not found in Library — playlist UI not integrated (only Liked Tracks + History present)</v>
+        <v>As expected</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>MODULE 7</v>
+        <v>MODULE 6</v>
       </c>
       <c r="B11" t="str">
-        <v>TC-PLY-002</v>
+        <v>TC-ENG-004</v>
       </c>
       <c r="C11" t="str">
-        <v>Create New Playlist button exists</v>
+        <v>Like button toggles on a track</v>
       </c>
       <c r="D11" t="str">
-        <v>LibraryScreen</v>
+        <v>FeedScreen / TrackDetail</v>
       </c>
       <c r="E11" t="str">
-        <v>Create Playlist FAB or button visible</v>
+        <v>Heart icon fills / Like count increments after tap</v>
       </c>
       <c r="F11" t="str">
         <v>❌ FAILED</v>
       </c>
       <c r="G11" t="str">
-        <v>CASCADE: MODULE 7 already failed — TC-PLY-002 auto-failed</v>
+        <v>Liked a track in Feed but no tracks found in Liked Tracks — like action not wired to backend</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>MODULE 7</v>
+        <v>MODULE 6</v>
       </c>
       <c r="B12" t="str">
-        <v>TC-PLY-003</v>
+        <v>TC-ENG-005</v>
       </c>
       <c r="C12" t="str">
-        <v>Playlist detail screen renders with tracks</v>
+        <v>Repost button exists on a track</v>
       </c>
       <c r="D12" t="str">
-        <v>PlaylistDetail</v>
+        <v>FeedScreen / TrackDetail</v>
       </c>
       <c r="E12" t="str">
-        <v>"Tracks" list or TrackTile visible</v>
+        <v>Repost / Share icon visible on track card</v>
       </c>
       <c r="F12" t="str">
         <v>❌ FAILED</v>
       </c>
       <c r="G12" t="str">
-        <v>CASCADE: MODULE 7 already failed — TC-PLY-003 auto-failed</v>
+        <v>Repost/Share button not found anywhere (Feed, TrackDetail, LikedTracks) — repost feature not integrated in Flutter UI</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>MODULE 8</v>
+        <v>MODULE 7</v>
       </c>
       <c r="B13" t="str">
-        <v>TC-SRCH-001</v>
+        <v>TC-PLY-001</v>
       </c>
       <c r="C13" t="str">
-        <v>Search screen renders with search bar</v>
+        <v>Playlists section exists in Library</v>
       </c>
       <c r="D13" t="str">
-        <v>SearchScreen</v>
+        <v>LibraryScreen</v>
       </c>
       <c r="E13" t="str">
-        <v>"Search Pulsify..." hint or category tabs visible</v>
+        <v>"Playlists" / "Sets" / "Collections" section visible</v>
       </c>
       <c r="F13" t="str">
-        <v>✅ PASSED</v>
+        <v>❌ FAILED</v>
       </c>
       <c r="G13" t="str">
-        <v>As expected</v>
+        <v>Playlists section not found in Library — playlist UI not integrated (only Liked Tracks + History present)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>MODULE 8</v>
+        <v>MODULE 7</v>
       </c>
       <c r="B14" t="str">
-        <v>TC-SRCH-002</v>
+        <v>TC-PLY-002</v>
       </c>
       <c r="C14" t="str">
-        <v>Category tabs (Tracks, Profiles) visible</v>
+        <v>Create New Playlist button exists</v>
       </c>
       <c r="D14" t="str">
-        <v>SearchScreen</v>
+        <v>LibraryScreen</v>
       </c>
       <c r="E14" t="str">
-        <v>"Tracks" and "Profiles" tabs visible</v>
+        <v>Create Playlist FAB or button visible</v>
       </c>
       <c r="F14" t="str">
-        <v>✅ PASSED</v>
+        <v>❌ FAILED</v>
       </c>
       <c r="G14" t="str">
-        <v>As expected</v>
+        <v>CASCADE: MODULE 7 already failed — TC-PLY-002 auto-failed</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>MODULE 8</v>
+        <v>MODULE 7</v>
       </c>
       <c r="B15" t="str">
-        <v>TC-SRCH-003</v>
+        <v>TC-PLY-003</v>
       </c>
       <c r="C15" t="str">
-        <v>Search "fuck it i love you" returns results or empty state</v>
+        <v>Playlist detail screen renders with tracks</v>
       </c>
       <c r="D15" t="str">
-        <v>SearchScreen → SearchResults</v>
+        <v>PlaylistDetail</v>
       </c>
       <c r="E15" t="str">
-        <v>TrackTile/ListTile results or "No results" message</v>
+        <v>"Tracks" list or TrackTile visible</v>
       </c>
       <c r="F15" t="str">
-        <v>✅ PASSED</v>
+        <v>❌ FAILED</v>
       </c>
       <c r="G15" t="str">
-        <v>As expected</v>
+        <v>CASCADE: MODULE 7 already failed — TC-PLY-003 auto-failed</v>
       </c>
     </row>
     <row r="16">
@@ -849,16 +849,16 @@
         <v>MODULE 8</v>
       </c>
       <c r="B16" t="str">
-        <v>TC-SRCH-004</v>
+        <v>TC-SRCH-001</v>
       </c>
       <c r="C16" t="str">
-        <v>Trending Now section visible on idle search</v>
+        <v>Search screen renders with search bar</v>
       </c>
       <c r="D16" t="str">
         <v>SearchScreen</v>
       </c>
       <c r="E16" t="str">
-        <v>"Trending Now" header or search bar visible</v>
+        <v>"Search Pulsify..." hint or category tabs visible</v>
       </c>
       <c r="F16" t="str">
         <v>✅ PASSED</v>
@@ -872,16 +872,16 @@
         <v>MODULE 8</v>
       </c>
       <c r="B17" t="str">
-        <v>TC-SRCH-005</v>
+        <v>TC-SRCH-002</v>
       </c>
       <c r="C17" t="str">
-        <v>Gibberish query shows empty state</v>
+        <v>Category tabs (Tracks, Profiles) visible</v>
       </c>
       <c r="D17" t="str">
         <v>SearchScreen</v>
       </c>
       <c r="E17" t="str">
-        <v>Empty-state text or zero TrackTile elements</v>
+        <v>"Tracks" and "Profiles" tabs visible</v>
       </c>
       <c r="F17" t="str">
         <v>✅ PASSED</v>
@@ -892,42 +892,42 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>MODULE 9</v>
+        <v>MODULE 8</v>
       </c>
       <c r="B18" t="str">
-        <v>TC-MSG-001</v>
+        <v>TC-SRCH-003</v>
       </c>
       <c r="C18" t="str">
-        <v>Activity screen opens from Home toolbar</v>
+        <v>Search "fuck it i love you" returns results or empty state</v>
       </c>
       <c r="D18" t="str">
-        <v>HomeScreen → Activity</v>
+        <v>SearchScreen → SearchResults</v>
       </c>
       <c r="E18" t="str">
-        <v>"Activity" / "Messages" / "Notifications" tabs visible</v>
+        <v>TrackTile/ListTile results or "No results" message</v>
       </c>
       <c r="F18" t="str">
-        <v>✅ PASSED</v>
+        <v>❌ FAILED</v>
       </c>
       <c r="G18" t="str">
-        <v>As expected</v>
+        <v>input.pressKeyCode is not a function</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>MODULE 9</v>
+        <v>MODULE 8</v>
       </c>
       <c r="B19" t="str">
-        <v>TC-MSG-002</v>
+        <v>TC-SRCH-004</v>
       </c>
       <c r="C19" t="str">
-        <v>Messages tab opens message list</v>
+        <v>Trending Now section visible on idle search</v>
       </c>
       <c r="D19" t="str">
-        <v>ActivityScreen &gt; Messages</v>
+        <v>SearchScreen</v>
       </c>
       <c r="E19" t="str">
-        <v>Message list or "No messages yet." empty state</v>
+        <v>"Trending Now" header or search bar visible</v>
       </c>
       <c r="F19" t="str">
         <v>✅ PASSED</v>
@@ -938,19 +938,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>MODULE 9</v>
+        <v>MODULE 8</v>
       </c>
       <c r="B20" t="str">
-        <v>TC-MSG-003</v>
+        <v>TC-SRCH-005</v>
       </c>
       <c r="C20" t="str">
-        <v>Navigate back to Home from Messages</v>
+        <v>Gibberish query shows empty state</v>
       </c>
       <c r="D20" t="str">
-        <v>Messages → Home</v>
+        <v>SearchScreen</v>
       </c>
       <c r="E20" t="str">
-        <v>nav_home_tab visible after back navigation</v>
+        <v>Empty-state text or zero TrackTile elements</v>
       </c>
       <c r="F20" t="str">
         <v>✅ PASSED</v>
@@ -961,19 +961,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>MODULE 10</v>
+        <v>MODULE 9</v>
       </c>
       <c r="B21" t="str">
-        <v>TC-NOTIF-001</v>
+        <v>TC-MSG-001</v>
       </c>
       <c r="C21" t="str">
-        <v>Notifications tab visible on Activity screen</v>
+        <v>Activity screen opens from Home toolbar</v>
       </c>
       <c r="D21" t="str">
-        <v>ActivityScreen</v>
+        <v>HomeScreen → Activity</v>
       </c>
       <c r="E21" t="str">
-        <v>"Notifications" tab visible</v>
+        <v>"Activity" / "Messages" / "Notifications" tabs visible</v>
       </c>
       <c r="F21" t="str">
         <v>✅ PASSED</v>
@@ -984,19 +984,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>MODULE 10</v>
+        <v>MODULE 9</v>
       </c>
       <c r="B22" t="str">
-        <v>TC-NOTIF-002</v>
+        <v>TC-MSG-002</v>
       </c>
       <c r="C22" t="str">
-        <v>Notifications list or empty state renders</v>
+        <v>Messages tab opens message list</v>
       </c>
       <c r="D22" t="str">
-        <v>ActivityScreen &gt; Notifications</v>
+        <v>ActivityScreen &gt; Messages</v>
       </c>
       <c r="E22" t="str">
-        <v>"Mark all as read" or empty state</v>
+        <v>Message list or "No messages yet." empty state</v>
       </c>
       <c r="F22" t="str">
         <v>✅ PASSED</v>
@@ -1007,16 +1007,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>MODULE 10</v>
+        <v>MODULE 9</v>
       </c>
       <c r="B23" t="str">
-        <v>TC-NOTIF-003</v>
+        <v>TC-MSG-003</v>
       </c>
       <c r="C23" t="str">
-        <v>Navigate back to Home from Notifications</v>
+        <v>Navigate back to Home from Messages</v>
       </c>
       <c r="D23" t="str">
-        <v>Notifications → Home</v>
+        <v>Messages → Home</v>
       </c>
       <c r="E23" t="str">
         <v>nav_home_tab visible after back navigation</v>
@@ -1030,88 +1030,88 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>MODULE 11</v>
+        <v>MODULE 9</v>
       </c>
       <c r="B24" t="str">
-        <v>TC-MOD-001</v>
+        <v>TC-MSG-004</v>
       </c>
       <c r="C24" t="str">
-        <v>"Report User" action accessible from track detail</v>
+        <v>Open a conversation thread with text input</v>
       </c>
       <c r="D24" t="str">
-        <v>LikedTracksScreen → TrackDetail</v>
+        <v>ActivityScreen &gt; Messages &gt; Thread</v>
       </c>
       <c r="E24" t="str">
-        <v>"Report User" / "Report" menu item visible</v>
+        <v>Message thread renders with text input field</v>
       </c>
       <c r="F24" t="str">
-        <v>❌ FAILED</v>
+        <v>✅ PASSED</v>
       </c>
       <c r="G24" t="str">
-        <v>No liked track to open — cannot test Report UI</v>
+        <v>As expected</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MODULE 11</v>
+        <v>MODULE 10</v>
       </c>
       <c r="B25" t="str">
-        <v>TC-MOD-002</v>
+        <v>TC-NOTIF-001</v>
       </c>
       <c r="C25" t="str">
-        <v>"Mute User" action accessible</v>
+        <v>Notifications tab visible on Activity screen</v>
       </c>
       <c r="D25" t="str">
-        <v>LikedTracksScreen → TrackDetail</v>
+        <v>ActivityScreen</v>
       </c>
       <c r="E25" t="str">
-        <v>"Mute" / "Mute User" menu item visible</v>
+        <v>"Notifications" tab visible</v>
       </c>
       <c r="F25" t="str">
-        <v>❌ FAILED</v>
+        <v>✅ PASSED</v>
       </c>
       <c r="G25" t="str">
-        <v>CASCADE: MODULE 11 already failed — TC-MOD-002 auto-failed</v>
+        <v>As expected</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>MODULE 11</v>
+        <v>MODULE 10</v>
       </c>
       <c r="B26" t="str">
-        <v>TC-MOD-003</v>
+        <v>TC-NOTIF-002</v>
       </c>
       <c r="C26" t="str">
-        <v>Report submitted shows confirmation</v>
+        <v>Notifications list or empty state renders</v>
       </c>
       <c r="D26" t="str">
-        <v>ReportDialog</v>
+        <v>ActivityScreen &gt; Notifications</v>
       </c>
       <c r="E26" t="str">
-        <v>Success snackbar or confirmation dialog</v>
+        <v>"Mark all as read" or empty state</v>
       </c>
       <c r="F26" t="str">
-        <v>❌ FAILED</v>
+        <v>✅ PASSED</v>
       </c>
       <c r="G26" t="str">
-        <v>CASCADE: MODULE 11 already failed — TC-MOD-003 auto-failed</v>
+        <v>As expected</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>MODULE 12</v>
+        <v>MODULE 10</v>
       </c>
       <c r="B27" t="str">
-        <v>TC-SUB-001</v>
+        <v>TC-NOTIF-003</v>
       </c>
       <c r="C27" t="str">
-        <v>Upgrade screen accessible via nav tab</v>
+        <v>Navigate back to Home from Notifications</v>
       </c>
       <c r="D27" t="str">
-        <v>MainScreen &gt; Upgrade</v>
+        <v>Notifications → Home</v>
       </c>
       <c r="E27" t="str">
-        <v>"Go Premium" or "Upgrade" text visible</v>
+        <v>nav_home_tab visible after back navigation</v>
       </c>
       <c r="F27" t="str">
         <v>✅ PASSED</v>
@@ -1122,145 +1122,260 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>MODULE 12</v>
+        <v>MODULE 10</v>
       </c>
       <c r="B28" t="str">
-        <v>TC-SUB-002</v>
+        <v>TC-NOTIF-004</v>
       </c>
       <c r="C28" t="str">
-        <v>Real subscription plans show pricing</v>
+        <v>Unread notification badge on Activity icon</v>
       </c>
       <c r="D28" t="str">
-        <v>UpgradeScreen</v>
+        <v>HomeScreen AppBar</v>
       </c>
       <c r="E28" t="str">
-        <v>"Monthly" / "Annual" / "/month" pricing visible</v>
+        <v>Badge/dot/number indicator on Activity icon when unread notifications exist</v>
       </c>
       <c r="F28" t="str">
-        <v>❌ FAILED</v>
+        <v>✅ PASSED</v>
       </c>
       <c r="G28" t="str">
-        <v>No subscription pricing plans found — screen is a "Coming soon" stub, real plans not integrated</v>
+        <v>As expected</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>MODULE 12</v>
+        <v>MODULE 11</v>
       </c>
       <c r="B29" t="str">
-        <v>TC-SUB-003</v>
+        <v>TC-MOD-001</v>
       </c>
       <c r="C29" t="str">
-        <v>Subscribe / Purchase button exists</v>
+        <v>"Report User" action accessible from track detail</v>
       </c>
       <c r="D29" t="str">
-        <v>UpgradeScreen</v>
+        <v>LikedTracksScreen → TrackDetail</v>
       </c>
       <c r="E29" t="str">
-        <v>"Subscribe" or "Get Premium" button visible</v>
+        <v>"Report User" / "Report" menu item visible</v>
       </c>
       <c r="F29" t="str">
         <v>❌ FAILED</v>
       </c>
       <c r="G29" t="str">
-        <v>CASCADE: MODULE 12 already failed — TC-SUB-003 auto-failed</v>
+        <v>No liked track to open — cannot test Report UI</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>MODULE 13</v>
+        <v>MODULE 11</v>
       </c>
       <c r="B30" t="str">
-        <v>TC-ALB-001</v>
+        <v>TC-MOD-002</v>
       </c>
       <c r="C30" t="str">
-        <v>Albums section accessible from Profile or Library</v>
+        <v>"Mute User" action accessible</v>
       </c>
       <c r="D30" t="str">
-        <v>ProfileScreen / LibraryScreen</v>
+        <v>LikedTracksScreen → TrackDetail</v>
       </c>
       <c r="E30" t="str">
-        <v>"Albums" tab or section visible</v>
+        <v>"Mute" / "Mute User" menu item visible</v>
       </c>
       <c r="F30" t="str">
         <v>❌ FAILED</v>
       </c>
       <c r="G30" t="str">
-        <v>Albums section not found in Profile or Library — Album feature not integrated (only data model exists)</v>
+        <v>CASCADE: MODULE 11 already failed — TC-MOD-002 auto-failed</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MODULE 13</v>
+        <v>MODULE 11</v>
       </c>
       <c r="B31" t="str">
-        <v>TC-ALB-002</v>
+        <v>TC-MOD-003</v>
       </c>
       <c r="C31" t="str">
-        <v>Create Album button present</v>
+        <v>Report submitted shows confirmation</v>
       </c>
       <c r="D31" t="str">
-        <v>AlbumsScreen</v>
+        <v>ReportDialog</v>
       </c>
       <c r="E31" t="str">
-        <v>"Create Album" FAB or button visible</v>
+        <v>Success snackbar or confirmation dialog</v>
       </c>
       <c r="F31" t="str">
         <v>❌ FAILED</v>
       </c>
       <c r="G31" t="str">
-        <v>CASCADE: MODULE 13 already failed — TC-ALB-002 auto-failed</v>
+        <v>CASCADE: MODULE 11 already failed — TC-MOD-003 auto-failed</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MODULE 13</v>
+        <v>MODULE 12</v>
       </c>
       <c r="B32" t="str">
-        <v>TC-ALB-003</v>
+        <v>TC-SUB-001</v>
       </c>
       <c r="C32" t="str">
-        <v>Album detail screen renders track list</v>
+        <v>Upgrade screen accessible via nav tab</v>
       </c>
       <c r="D32" t="str">
-        <v>AlbumDetail</v>
+        <v>MainScreen &gt; Upgrade</v>
       </c>
       <c r="E32" t="str">
-        <v>"Tracks" list or TrackTile visible</v>
+        <v>"Go Premium" or "Upgrade" text visible</v>
       </c>
       <c r="F32" t="str">
-        <v>❌ FAILED</v>
+        <v>✅ PASSED</v>
       </c>
       <c r="G32" t="str">
-        <v>CASCADE: MODULE 13 already failed — TC-ALB-003 auto-failed</v>
+        <v>As expected</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v>MODULE 12</v>
+      </c>
+      <c r="B33" t="str">
+        <v>TC-SUB-002</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Real subscription plans show pricing</v>
+      </c>
+      <c r="D33" t="str">
+        <v>UpgradeScreen</v>
+      </c>
+      <c r="E33" t="str">
+        <v>"Monthly" / "Annual" / "/month" pricing visible</v>
+      </c>
+      <c r="F33" t="str">
+        <v>❌ FAILED</v>
+      </c>
+      <c r="G33" t="str">
+        <v>No subscription pricing plans found — screen is a "Coming soon" stub, real plans not integrated</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>MODULE 12</v>
+      </c>
+      <c r="B34" t="str">
+        <v>TC-SUB-003</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Subscribe / Purchase button exists</v>
+      </c>
+      <c r="D34" t="str">
+        <v>UpgradeScreen</v>
+      </c>
+      <c r="E34" t="str">
+        <v>"Subscribe" or "Get Premium" button visible</v>
+      </c>
+      <c r="F34" t="str">
+        <v>❌ FAILED</v>
+      </c>
+      <c r="G34" t="str">
+        <v>CASCADE: MODULE 12 already failed — TC-SUB-003 auto-failed</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>MODULE 13</v>
+      </c>
+      <c r="B35" t="str">
+        <v>TC-ALB-001</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Albums section accessible from Profile or Library</v>
+      </c>
+      <c r="D35" t="str">
+        <v>ProfileScreen / LibraryScreen</v>
+      </c>
+      <c r="E35" t="str">
+        <v>"Albums" tab or section visible</v>
+      </c>
+      <c r="F35" t="str">
+        <v>❌ FAILED</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Albums section not found in Profile or Library — Album feature not integrated (only data model exists)</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>MODULE 13</v>
+      </c>
+      <c r="B36" t="str">
+        <v>TC-ALB-002</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Create Album button present</v>
+      </c>
+      <c r="D36" t="str">
+        <v>AlbumsScreen</v>
+      </c>
+      <c r="E36" t="str">
+        <v>"Create Album" FAB or button visible</v>
+      </c>
+      <c r="F36" t="str">
+        <v>❌ FAILED</v>
+      </c>
+      <c r="G36" t="str">
+        <v>CASCADE: MODULE 13 already failed — TC-ALB-002 auto-failed</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>MODULE 13</v>
+      </c>
+      <c r="B37" t="str">
+        <v>TC-ALB-003</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Album detail screen renders track list</v>
+      </c>
+      <c r="D37" t="str">
+        <v>AlbumDetail</v>
+      </c>
+      <c r="E37" t="str">
+        <v>"Tracks" list or TrackTile visible</v>
+      </c>
+      <c r="F37" t="str">
+        <v>❌ FAILED</v>
+      </c>
+      <c r="G37" t="str">
+        <v>CASCADE: MODULE 13 already failed — TC-ALB-003 auto-failed</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
         <v>CLEANUP</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B38" t="str">
         <v>TC-LOGOUT-001</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C38" t="str">
         <v>Logout from Profile screen</v>
       </c>
-      <c r="D33" t="str">
+      <c r="D38" t="str">
         <v>ProfileScreen</v>
       </c>
-      <c r="E33" t="str">
+      <c r="E38" t="str">
         <v>Login screen appears after logout</v>
       </c>
-      <c r="F33" t="str">
-        <v>✅ PASSED</v>
-      </c>
-      <c r="G33" t="str">
+      <c r="F38" t="str">
+        <v>✅ PASSED</v>
+      </c>
+      <c r="G38" t="str">
         <v>As expected</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G38"/>
   </ignoredErrors>
 </worksheet>
 </file>
